--- a/docs/example/example-report.xlsx
+++ b/docs/example/example-report.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="168" formatCode="DD.MM.YYYY"/>
     <numFmt numFmtId="169" formatCode="#,##0.###"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,16 +39,24 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <color rgb="006B7280"/>
+    </font>
+    <font>
       <color rgb="000563C1"/>
       <u val="single"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="002B2D42"/>
       <sz val="16"/>
-    </font>
-    <font>
-      <color rgb="006B7280"/>
     </font>
     <font>
       <b val="1"/>
@@ -86,12 +94,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -106,10 +114,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -127,9 +144,9 @@
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -210,22 +227,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Notices" displayName="Notices" ref="A1:M15" headerRowCount="1">
-  <autoFilter ref="A1:M15"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Notices" displayName="Notices" ref="A1:N15" headerRowCount="1">
+  <autoFilter ref="A1:N15"/>
+  <tableColumns count="14">
     <tableColumn id="1" name="№ закупки"/>
     <tableColumn id="2" name="Название"/>
     <tableColumn id="3" name="Почему подошла"/>
     <tableColumn id="4" name="Начальная цена"/>
     <tableColumn id="5" name="Подача заявок до"/>
     <tableColumn id="6" name="Часовой пояс"/>
-    <tableColumn id="7" name="Способ"/>
-    <tableColumn id="8" name="Заказчик"/>
-    <tableColumn id="9" name="ИНН заказчика"/>
-    <tableColumn id="10" name="Регион"/>
-    <tableColumn id="11" name="Площадка"/>
-    <tableColumn id="12" name="Размещено"/>
-    <tableColumn id="13" name="Примечание"/>
+    <tableColumn id="7" name="Этап"/>
+    <tableColumn id="8" name="Способ"/>
+    <tableColumn id="9" name="Заказчик"/>
+    <tableColumn id="10" name="ИНН заказчика"/>
+    <tableColumn id="11" name="Регион"/>
+    <tableColumn id="12" name="Площадка"/>
+    <tableColumn id="13" name="Размещено"/>
+    <tableColumn id="14" name="Примечание"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
@@ -539,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -548,13 +566,14 @@
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -590,35 +609,40 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Способ</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Заказчик</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ИНН заказчика</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Регион</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Площадка</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Размещено</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
@@ -652,35 +676,40 @@
           <t>МСК+2</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Определение поставщика завершено</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Запрос котировок в электронной форме</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>ДЕПАРТАМЕНТ ЗЕМЕЛЬНЫХ ОТНОШЕНИЙ И ГРАДОСТРОИТЕЛЬСТВА АДМИНИСТРАЦИИ ГОРОДА ТЮМЕНИ</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>7202029213</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>Тюменская область</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>РТС-тендер</t>
         </is>
       </c>
-      <c r="L2" s="7" t="n">
+      <c r="M2" s="8" t="n">
         <v>46273</v>
       </c>
-      <c r="M2" s="3" t="n"/>
+      <c r="N2" s="3" t="n"/>
     </row>
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -710,35 +739,40 @@
           <t>МСК+2</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Определение поставщика завершено</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Электронный аукцион</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>УПРАВЛЕНИЕ ПО ОБЕСПЕЧЕНИЮ ДЕЯТЕЛЬНОСТИ МИРОВЫХ СУДЕЙ В ТЮМЕНСКОЙ ОБЛАСТИ</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>7202100787</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Тюменская область</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>РОСЭЛТОРГ (АО«ЕЭТП»)</t>
         </is>
       </c>
-      <c r="L3" s="7" t="n">
+      <c r="M3" s="8" t="n">
         <v>46273</v>
       </c>
-      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -768,35 +802,40 @@
           <t>МСК+2</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Определение поставщика завершено</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Запрос котировок в электронной форме</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>ДЕПАРТАМЕНТ ЗЕМЕЛЬНЫХ ОТНОШЕНИЙ И ГРАДОСТРОИТЕЛЬСТВА АДМИНИСТРАЦИИ ГОРОДА ТЮМЕНИ</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>7202029213</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Тюменская область</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>РТС-тендер</t>
         </is>
       </c>
-      <c r="L4" s="7" t="n">
+      <c r="M4" s="8" t="n">
         <v>46274</v>
       </c>
-      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
     </row>
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -830,35 +869,40 @@
           <t>МСК+2</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Определение поставщика завершено</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Запрос котировок в электронной форме</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>УПРАВЛЕНИЕ ДЕЛАМИ ПРАВИТЕЛЬСТВА ТЮМЕНСКОЙ ОБЛАСТИ</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>7202137025</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Тюменская область</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>АО «Сбербанк-АСТ»</t>
         </is>
       </c>
-      <c r="L5" s="7" t="n">
+      <c r="M5" s="8" t="n">
         <v>46275</v>
       </c>
-      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -889,35 +933,40 @@
           <t>МСК+2</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Определение поставщика завершено</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Запрос котировок в электронной форме</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>ДЕПАРТАМЕНТ ЗЕМЕЛЬНЫХ ОТНОШЕНИЙ И ГРАДОСТРОИТЕЛЬСТВА АДМИНИСТРАЦИИ ГОРОДА ТЮМЕНИ</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>7202029213</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>Тюменская область</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>РТС-тендер</t>
         </is>
       </c>
-      <c r="L6" s="7" t="n">
+      <c r="M6" s="8" t="n">
         <v>46280</v>
       </c>
-      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -947,35 +996,40 @@
           <t>МСК+2</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Определение поставщика завершено</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Электронный аукцион</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>ФЕДЕРАЛЬНОЕ КАЗЕННОЕ УЧРЕЖДЕНИЕ "ИСПРАВИТЕЛЬНАЯ КОЛОНИЯ № 4 УПРАВЛЕНИЯ ФЕДЕРАЛЬНОЙ СЛУЖБЫ ИСПОЛНЕНИЯ НАКАЗАНИЙ ПО ТЮМЕНСКОЙ ОБЛАСТИ"</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>7204004694</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>Тюменская область</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>АО «Сбербанк-АСТ»</t>
         </is>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="M7" s="8" t="n">
         <v>46281</v>
       </c>
-      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1010,35 +1064,40 @@
           <t>МСК+2</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Определение поставщика завершено</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Электронный аукцион</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>УПРАВЛЕНИЕ ДЕЛАМИ ПРАВИТЕЛЬСТВА ТЮМЕНСКОЙ ОБЛАСТИ</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>7202137025</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>Тюменская область</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>АО «Сбербанк-АСТ»</t>
         </is>
       </c>
-      <c r="L8" s="7" t="n">
+      <c r="M8" s="8" t="n">
         <v>46282</v>
       </c>
-      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="n"/>
     </row>
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -1067,35 +1126,40 @@
           <t>МСК+2</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Работа комиссии</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Запрос котировок в электронной форме</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>ГОСУДАРСТВЕННОЕ БЮДЖЕТНОЕ УЧРЕЖДЕНИЕ ЗДРАВООХРАНЕНИЯ ТЮМЕНСКОЙ ОБЛАСТИ "ОБЛАСТНОЕ БЮРО СУДЕБНО-МЕДИЦИНСКОЙ ЭКСПЕРТИЗЫ"</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>7203058175</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>Тюменская область</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>АО «Сбербанк-АСТ»</t>
         </is>
       </c>
-      <c r="L9" s="7" t="n">
+      <c r="M9" s="8" t="n">
         <v>46286</v>
       </c>
-      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1125,35 +1189,40 @@
           <t>МСК+2</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Определение поставщика завершено</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Электронный аукцион</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>ОТДЕЛ ОБРАЗОВАНИЯ АДМИНИСТРАЦИИ АБАТСКОГО МУНИЦИПАЛЬНОГО ОКРУГА</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>7208003596</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>Тюменская область</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>ЭТП ТЭК-Торг</t>
         </is>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="M10" s="8" t="n">
         <v>46283</v>
       </c>
-      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="n"/>
     </row>
     <row r="11" ht="105" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -1188,35 +1257,40 @@
           <t>МСК+2</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Электронный аукцион</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>СЕВЕРО-УРАЛЬСКОЕ УПРАВЛЕНИЕ ФЕДЕРАЛЬНОЙ СЛУЖБЫ ПО ЭКОЛОГИЧЕСКОМУ, ТЕХНОЛОГИЧЕСКОМУ И АТОМНОМУ НАДЗОРУ</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>7202022112</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>Тюменская область</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>АО «Сбербанк-АСТ»</t>
         </is>
       </c>
-      <c r="L11" s="7" t="n">
-        <v>46293</v>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" s="8" t="n">
+        <v>46288</v>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>редакция 3</t>
         </is>
@@ -1255,35 +1329,40 @@
           <t>МСК+2</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Электронный аукцион</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>СЕВЕРО-УРАЛЬСКОЕ УПРАВЛЕНИЕ ФЕДЕРАЛЬНОЙ СЛУЖБЫ ПО ЭКОЛОГИЧЕСКОМУ, ТЕХНОЛОГИЧЕСКОМУ И АТОМНОМУ НАДЗОРУ</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>7202022112</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>Тюменская область</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>АО «Сбербанк-АСТ»</t>
         </is>
       </c>
-      <c r="L12" s="7" t="n">
-        <v>46288</v>
-      </c>
-      <c r="M12" s="3" t="n"/>
+      <c r="M12" s="8" t="n">
+        <v>46290</v>
+      </c>
+      <c r="N12" s="3" t="n"/>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -1313,35 +1392,40 @@
           <t>МСК+2</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Электронный аукцион</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>АДМИНИСТРАЦИЯ ЯЛУТОРОВСКОГО МУНИЦИПАЛЬНОГО ОКРУГА</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>7207007534</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>Тюменская область</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>РОСЭЛТОРГ (АО«ЕЭТП»)</t>
         </is>
       </c>
-      <c r="L13" s="7" t="n">
+      <c r="M13" s="8" t="n">
         <v>46295</v>
       </c>
-      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1371,35 +1455,40 @@
           <t>МСК+2</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Электронный аукцион</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>ФЕДЕРАЛЬНОЕ КАЗЕННОЕ УЧРЕЖДЕНИЕ "ИСПРАВИТЕЛЬНАЯ КОЛОНИЯ № 2 УПРАВЛЕНИЯ ФЕДЕРАЛЬНОЙ СЛУЖБЫ ИСПОЛНЕНИЯ НАКАЗАНИЙ ПО ТЮМЕНСКОЙ ОБЛАСТИ"</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>7203096090</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>Тюменская область</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>АО «Сбербанк-АСТ»</t>
         </is>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="M14" s="8" t="n">
         <v>46296</v>
       </c>
-      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="3" t="n"/>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -1429,35 +1518,40 @@
           <t>МСК+2</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Электронный аукцион</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>АРБИТРАЖНЫЙ СУД ТЮМЕНСКОЙ ОБЛАСТИ</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>7202057669</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>Тюменская область</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>АО «Сбербанк-АСТ»</t>
         </is>
       </c>
-      <c r="L15" s="7" t="n">
-        <v>46295</v>
-      </c>
-      <c r="M15" s="3" t="n"/>
+      <c r="M15" s="8" t="n">
+        <v>46297</v>
+      </c>
+      <c r="N15" s="3" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1557,46 +1651,46 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>0167300000526000648</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>Файл-вкладыш</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000-00000054</t>
         </is>
       </c>
-      <c r="G2" s="11" t="n">
+      <c r="G2" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>Упаковка</t>
         </is>
       </c>
-      <c r="I2" s="12" t="n">
+      <c r="I2" s="15" t="n">
         <v>625.1</v>
       </c>
-      <c r="J2" s="12" t="n">
+      <c r="J2" s="15" t="n">
         <v>62510</v>
       </c>
     </row>
@@ -1625,7 +1719,7 @@
           <t>22.29.21.000-00000002</t>
         </is>
       </c>
-      <c r="G3" s="13" t="n">
+      <c r="G3" s="16" t="n">
         <v>50</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -1641,134 +1735,134 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>0167200003426007383</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>Бумага для офисной техники</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>17.12.14.110</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>17.12.14.110-00000003</t>
         </is>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="G4" s="14" t="n">
         <v>20000</v>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t>Пачка</t>
         </is>
       </c>
-      <c r="I4" s="12" t="n">
+      <c r="I4" s="15" t="n">
         <v>331.84</v>
       </c>
-      <c r="J4" s="12" t="n">
+      <c r="J4" s="15" t="n">
         <v>6636800</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>0167300000526000657</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Бумага для офисной техники</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>17.12.14.110</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>17.12.14.110-00000002</t>
         </is>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="14" t="n">
         <v>198</v>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>Пачка</t>
         </is>
       </c>
-      <c r="I5" s="12" t="n">
+      <c r="I5" s="15" t="n">
         <v>367.26</v>
       </c>
-      <c r="J5" s="12" t="n">
+      <c r="J5" s="15" t="n">
         <v>72717.48</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>0167200003426007464</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>Ручка канцелярская</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>32.99.12.110</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>32.99.12.110-00000002</t>
         </is>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I6" s="12" t="n">
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="n">
         <v>56</v>
       </c>
-      <c r="J6" s="12" t="n">
+      <c r="J6" s="15" t="n">
         <v>16800</v>
       </c>
     </row>
@@ -1793,7 +1887,7 @@
         </is>
       </c>
       <c r="F7" s="6" t="n"/>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="16" t="n">
         <v>30</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -1809,46 +1903,46 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>0167200003426007464</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>Ручка канцелярская</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>32.99.12.110</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>32.99.12.110-00000007</t>
         </is>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="n">
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="J8" s="12" t="n">
+      <c r="J8" s="15" t="n">
         <v>45000</v>
       </c>
     </row>
@@ -1877,7 +1971,7 @@
           <t>25.71.13.110-00000001</t>
         </is>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="16" t="n">
         <v>200</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1913,7 +2007,7 @@
         </is>
       </c>
       <c r="F10" s="6" t="n"/>
-      <c r="G10" s="13" t="n">
+      <c r="G10" s="16" t="n">
         <v>80</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1929,46 +2023,46 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>0167200003426007464</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Маркер</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>32.99.12.120</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>32.99.12.120-00000006</t>
         </is>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G11" s="14" t="n">
         <v>400</v>
       </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I11" s="12" t="n">
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="J11" s="15" t="n">
         <v>14000</v>
       </c>
     </row>
@@ -1997,7 +2091,7 @@
           <t>25.71.13.110-00000004</t>
         </is>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="G12" s="16" t="n">
         <v>250</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -2013,266 +2107,266 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>0167200003426007464</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B13" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Ручка канцелярская</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>32.99.12.110</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>32.99.12.110-00000003</t>
         </is>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="n">
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="n">
         <v>251</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="J13" s="15" t="n">
         <v>50200</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>0167200003426007464</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>Ручка канцелярская</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>32.99.12.110</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>32.99.12.110-00000005</t>
         </is>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="G14" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="n">
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="J14" s="15" t="n">
         <v>3400</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>0167300000526000676</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>Скобы для степлера</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000-00000007</t>
         </is>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="14" t="n">
         <v>400</v>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="13" t="inlineStr">
         <is>
           <t>Упаковка</t>
         </is>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="I15" s="15" t="n">
         <v>32.73</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="J15" s="15" t="n">
         <v>13092</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>0167300000526000676</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Степлер</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>25.99.22.130</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>25.99.22.130-00000007</t>
         </is>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="G16" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I16" s="12" t="n">
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="n">
         <v>158.19</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="J16" s="15" t="n">
         <v>7909.5</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>0367100010126000046</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B17" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Бумага для офисной техники</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>17.12.14.110</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>17.12.14.110-00000005</t>
         </is>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="14" t="n">
         <v>315</v>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t>Пачка</t>
         </is>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="I17" s="15" t="n">
         <v>378.39</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="J17" s="15" t="n">
         <v>119192.85</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>0167200003426007669</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Клейкие закладки пластиковые</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000-00000002</t>
         </is>
       </c>
-      <c r="G18" s="11" t="n">
+      <c r="G18" s="14" t="n">
         <v>3000</v>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="13" t="inlineStr">
         <is>
           <t>Упаковка</t>
         </is>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="I18" s="15" t="n">
         <v>31</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="J18" s="15" t="n">
         <v>93000</v>
       </c>
     </row>
@@ -2297,7 +2391,7 @@
         </is>
       </c>
       <c r="F19" s="6" t="n"/>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="16" t="n">
         <v>100</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -2337,7 +2431,7 @@
           <t>20.59.59.900-00000001</t>
         </is>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="G20" s="16" t="n">
         <v>1500</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2353,266 +2447,266 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>0167200003426007669</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n">
+      <c r="B21" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Файл-вкладыш</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000-00000013</t>
         </is>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="G21" s="14" t="n">
         <v>80000</v>
       </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I21" s="12" t="n">
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="n">
         <v>3.2</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="J21" s="15" t="n">
         <v>256000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>0167200003426007669</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>Папка картонная</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>17.23.13.193</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>17.23.13.193-00000010</t>
         </is>
       </c>
-      <c r="G22" s="11" t="n">
+      <c r="G22" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="n">
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="n">
         <v>221</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="J22" s="15" t="n">
         <v>66300</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>0167200003426007669</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n">
+      <c r="B23" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Тетрадь различного назначения</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>17.23.13.196</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>17.23.13.196-00000001</t>
         </is>
       </c>
-      <c r="G23" s="11" t="n">
+      <c r="G23" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I23" s="12" t="n">
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="n">
         <v>107</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="J23" s="15" t="n">
         <v>10700</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>0167200003426007669</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B24" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Тетрадь различного назначения</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>17.23.13.196</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>17.23.13.196-00000001</t>
         </is>
       </c>
-      <c r="G24" s="11" t="n">
+      <c r="G24" s="14" t="n">
         <v>250</v>
       </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I24" s="12" t="n">
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="n">
         <v>56</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="J24" s="15" t="n">
         <v>14000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>0167200003426007669</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n">
+      <c r="B25" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>Файл-вкладыш</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000-00000013</t>
         </is>
       </c>
-      <c r="G25" s="11" t="n">
+      <c r="G25" s="14" t="n">
         <v>8000</v>
       </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I25" s="12" t="n">
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="n">
         <v>51</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="J25" s="15" t="n">
         <v>408000</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>0167200003426007669</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n">
+      <c r="B26" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>Папка пластиковая</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000-00000004</t>
         </is>
       </c>
-      <c r="G26" s="11" t="n">
+      <c r="G26" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I26" s="12" t="n">
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I26" s="15" t="n">
         <v>121</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="J26" s="15" t="n">
         <v>18150</v>
       </c>
     </row>
@@ -2641,7 +2735,7 @@
           <t>22.29.21.000-00000001</t>
         </is>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="G27" s="16" t="n">
         <v>300</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -2657,46 +2751,46 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>0167200003426007669</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n">
+      <c r="B28" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>Блоки для записей</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>17.23.13.199</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>17.23.13.199-00000003</t>
         </is>
       </c>
-      <c r="G28" s="11" t="n">
+      <c r="G28" s="14" t="n">
         <v>2000</v>
       </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I28" s="12" t="n">
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="n">
         <v>38</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="J28" s="15" t="n">
         <v>76000</v>
       </c>
     </row>
@@ -2725,7 +2819,7 @@
           <t>20.59.59.900-00000003</t>
         </is>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="G29" s="16" t="n">
         <v>80</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -2741,46 +2835,46 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>0167200003426007669</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n">
+      <c r="B30" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>Папка картонная</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>17.23.13.193</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr">
         <is>
           <t>17.23.13.193-00000006</t>
         </is>
       </c>
-      <c r="G30" s="11" t="n">
+      <c r="G30" s="14" t="n">
         <v>2000</v>
       </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I30" s="12" t="n">
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I30" s="15" t="n">
         <v>26</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="J30" s="15" t="n">
         <v>52000</v>
       </c>
     </row>
@@ -2809,7 +2903,7 @@
           <t>25.71.11.120-00000004</t>
         </is>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="16" t="n">
         <v>300</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -2825,442 +2919,442 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>0167200003426007669</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n">
+      <c r="B32" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>Папка пластиковая</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F32" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000-00000008</t>
         </is>
       </c>
-      <c r="G32" s="11" t="n">
+      <c r="G32" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I32" s="12" t="n">
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I32" s="15" t="n">
         <v>119</v>
       </c>
-      <c r="J32" s="12" t="n">
+      <c r="J32" s="15" t="n">
         <v>35700</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>0167200003426007669</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n">
+      <c r="B33" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>Блоки для записей</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>17.23.13.199</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr">
         <is>
           <t>17.23.13.199-00000003</t>
         </is>
       </c>
-      <c r="G33" s="11" t="n">
+      <c r="G33" s="14" t="n">
         <v>600</v>
       </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I33" s="12" t="n">
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I33" s="15" t="n">
         <v>41</v>
       </c>
-      <c r="J33" s="12" t="n">
+      <c r="J33" s="15" t="n">
         <v>24600</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>0167200003426007669</t>
         </is>
       </c>
-      <c r="B34" s="9" t="n">
+      <c r="B34" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>Папка картонная</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>17.23.13.193</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>17.23.13.193-00000007</t>
         </is>
       </c>
-      <c r="G34" s="11" t="n">
+      <c r="G34" s="14" t="n">
         <v>15000</v>
       </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I34" s="12" t="n">
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I34" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="J34" s="12" t="n">
+      <c r="J34" s="15" t="n">
         <v>255000</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>0167200003426007669</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n">
+      <c r="B35" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C35" s="13" t="inlineStr">
         <is>
           <t>Папка пластиковая</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000-00000004</t>
         </is>
       </c>
-      <c r="G35" s="11" t="n">
+      <c r="G35" s="14" t="n">
         <v>250</v>
       </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I35" s="12" t="n">
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I35" s="15" t="n">
         <v>157</v>
       </c>
-      <c r="J35" s="12" t="n">
+      <c r="J35" s="15" t="n">
         <v>39250</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>0167200003426007669</t>
         </is>
       </c>
-      <c r="B36" s="9" t="n">
+      <c r="B36" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>Блоки для записей</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>17.23.13.199</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>17.23.13.199-00000003</t>
         </is>
       </c>
-      <c r="G36" s="11" t="n">
+      <c r="G36" s="14" t="n">
         <v>1000</v>
       </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I36" s="12" t="n">
+      <c r="H36" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I36" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="J36" s="12" t="n">
+      <c r="J36" s="15" t="n">
         <v>28000</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>0167200003426007669</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n">
+      <c r="B37" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C37" s="13" t="inlineStr">
         <is>
           <t>Лоток для бумаги пластиковый</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F37" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000-00000014</t>
         </is>
       </c>
-      <c r="G37" s="11" t="n">
+      <c r="G37" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I37" s="12" t="n">
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I37" s="15" t="n">
         <v>272</v>
       </c>
-      <c r="J37" s="12" t="n">
+      <c r="J37" s="15" t="n">
         <v>27200</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>0167200003426007669</t>
         </is>
       </c>
-      <c r="B38" s="9" t="n">
+      <c r="B38" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>Папка пластиковая</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000-00000008</t>
         </is>
       </c>
-      <c r="G38" s="11" t="n">
+      <c r="G38" s="14" t="n">
         <v>3000</v>
       </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I38" s="12" t="n">
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I38" s="15" t="n">
         <v>36</v>
       </c>
-      <c r="J38" s="12" t="n">
+      <c r="J38" s="15" t="n">
         <v>108000</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>0167200003426007669</t>
         </is>
       </c>
-      <c r="B39" s="9" t="n">
+      <c r="B39" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C39" s="13" t="inlineStr">
         <is>
           <t>Тетрадь различного назначения</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>17.23.13.196</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F39" s="12" t="inlineStr">
         <is>
           <t>17.23.13.196-00000001</t>
         </is>
       </c>
-      <c r="G39" s="11" t="n">
+      <c r="G39" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="H39" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I39" s="12" t="n">
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I39" s="15" t="n">
         <v>68</v>
       </c>
-      <c r="J39" s="12" t="n">
+      <c r="J39" s="15" t="n">
         <v>10200</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>0167200003426007731</t>
         </is>
       </c>
-      <c r="B40" s="9" t="n">
+      <c r="B40" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>Бумага для офисной техники</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>17.12.14.110</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>17.12.14.110-00000002</t>
         </is>
       </c>
-      <c r="G40" s="11" t="n">
+      <c r="G40" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H40" s="13" t="inlineStr">
         <is>
           <t>Пачка</t>
         </is>
       </c>
-      <c r="I40" s="12" t="n">
+      <c r="I40" s="15" t="n">
         <v>330</v>
       </c>
-      <c r="J40" s="12" t="n">
+      <c r="J40" s="15" t="n">
         <v>99000</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>0167300029226000067</t>
         </is>
       </c>
-      <c r="B41" s="9" t="n">
+      <c r="B41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C41" s="13" t="inlineStr">
         <is>
           <t>Бумага для офисной техники</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>17.12.14.110</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F41" s="12" t="inlineStr">
         <is>
           <t>17.12.14.110-00000005</t>
         </is>
       </c>
-      <c r="G41" s="11" t="n">
+      <c r="G41" s="14" t="n">
         <v>115</v>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H41" s="13" t="inlineStr">
         <is>
           <t>Пачка</t>
         </is>
       </c>
-      <c r="I41" s="12" t="n">
+      <c r="I41" s="15" t="n">
         <v>406.93</v>
       </c>
-      <c r="J41" s="12" t="n">
+      <c r="J41" s="15" t="n">
         <v>46796.95</v>
       </c>
     </row>
@@ -3289,7 +3383,7 @@
           <t>20.59.11.130-00000002</t>
         </is>
       </c>
-      <c r="G42" s="13" t="n">
+      <c r="G42" s="16" t="n">
         <v>2</v>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -3305,310 +3399,310 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B43" s="9" t="n">
+      <c r="B43" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C43" s="13" t="inlineStr">
         <is>
           <t>Ручка канцелярская</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>32.99.12.110</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F43" s="12" t="inlineStr">
         <is>
           <t>32.99.12.110-00000005</t>
         </is>
       </c>
-      <c r="G43" s="11" t="n">
+      <c r="G43" s="14" t="n">
         <v>320</v>
       </c>
-      <c r="H43" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I43" s="12" t="n">
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I43" s="15" t="n">
         <v>12.71</v>
       </c>
-      <c r="J43" s="12" t="n">
+      <c r="J43" s="15" t="n">
         <v>4067.2</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n">
+      <c r="B44" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C44" s="13" t="inlineStr">
         <is>
           <t>Маркер</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>32.99.12.120</t>
         </is>
       </c>
-      <c r="F44" s="9" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>32.99.12.120-00000006</t>
         </is>
       </c>
-      <c r="G44" s="11" t="n">
+      <c r="G44" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="H44" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I44" s="12" t="n">
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I44" s="15" t="n">
         <v>24.46</v>
       </c>
-      <c r="J44" s="12" t="n">
+      <c r="J44" s="15" t="n">
         <v>611.5</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B45" s="9" t="n">
+      <c r="B45" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C45" s="13" t="inlineStr">
         <is>
           <t>Ручка канцелярская</t>
         </is>
       </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E45" s="9" t="inlineStr">
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>32.99.12.110</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>32.99.12.110-00000008</t>
         </is>
       </c>
-      <c r="G45" s="11" t="n">
+      <c r="G45" s="14" t="n">
         <v>320</v>
       </c>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I45" s="12" t="n">
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I45" s="15" t="n">
         <v>42.75</v>
       </c>
-      <c r="J45" s="12" t="n">
+      <c r="J45" s="15" t="n">
         <v>13680</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B46" s="9" t="n">
+      <c r="B46" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C46" s="13" t="inlineStr">
         <is>
           <t>Ручка канцелярская</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E46" s="9" t="inlineStr">
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>32.99.12.110</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
+      <c r="F46" s="12" t="inlineStr">
         <is>
           <t>32.99.12.110-00000008</t>
         </is>
       </c>
-      <c r="G46" s="11" t="n">
+      <c r="G46" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I46" s="12" t="n">
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I46" s="15" t="n">
         <v>95.31999999999999</v>
       </c>
-      <c r="J46" s="12" t="n">
+      <c r="J46" s="15" t="n">
         <v>4766</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B47" s="9" t="n">
+      <c r="B47" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="C47" s="10" t="inlineStr">
+      <c r="C47" s="13" t="inlineStr">
         <is>
           <t>Папка пластиковая</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E47" s="9" t="inlineStr">
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F47" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000-00000005</t>
         </is>
       </c>
-      <c r="G47" s="11" t="n">
+      <c r="G47" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="H47" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I47" s="12" t="n">
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I47" s="15" t="n">
         <v>1875.03</v>
       </c>
-      <c r="J47" s="12" t="n">
+      <c r="J47" s="15" t="n">
         <v>3750.06</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B48" s="9" t="n">
+      <c r="B48" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C48" s="13" t="inlineStr">
         <is>
           <t>Маркер</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E48" s="9" t="inlineStr">
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>32.99.12.120</t>
         </is>
       </c>
-      <c r="F48" s="9" t="inlineStr">
+      <c r="F48" s="12" t="inlineStr">
         <is>
           <t>32.99.12.120-00000005</t>
         </is>
       </c>
-      <c r="G48" s="11" t="n">
+      <c r="G48" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="H48" s="13" t="inlineStr">
         <is>
           <t>Набор</t>
         </is>
       </c>
-      <c r="I48" s="12" t="n">
+      <c r="I48" s="15" t="n">
         <v>79.53</v>
       </c>
-      <c r="J48" s="12" t="n">
+      <c r="J48" s="15" t="n">
         <v>795.3</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B49" s="9" t="n">
+      <c r="B49" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="C49" s="10" t="inlineStr">
+      <c r="C49" s="13" t="inlineStr">
         <is>
           <t>Ручка канцелярская</t>
         </is>
       </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E49" s="9" t="inlineStr">
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>32.99.12.110</t>
         </is>
       </c>
-      <c r="F49" s="9" t="inlineStr">
+      <c r="F49" s="12" t="inlineStr">
         <is>
           <t>32.99.12.110-00000005</t>
         </is>
       </c>
-      <c r="G49" s="11" t="n">
+      <c r="G49" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="H49" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I49" s="12" t="n">
+      <c r="H49" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I49" s="15" t="n">
         <v>12.71</v>
       </c>
-      <c r="J49" s="12" t="n">
+      <c r="J49" s="15" t="n">
         <v>317.75</v>
       </c>
     </row>
@@ -3637,7 +3731,7 @@
           <t>13.10.85.110-00000002</t>
         </is>
       </c>
-      <c r="G50" s="13" t="n">
+      <c r="G50" s="16" t="n">
         <v>3</v>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -3653,46 +3747,46 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B51" s="9" t="n">
+      <c r="B51" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="C51" s="10" t="inlineStr">
+      <c r="C51" s="13" t="inlineStr">
         <is>
           <t>Маркер</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>32.99.12.120</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="F51" s="12" t="inlineStr">
         <is>
           <t>32.99.12.120-00000005</t>
         </is>
       </c>
-      <c r="G51" s="11" t="n">
+      <c r="G51" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="H51" s="13" t="inlineStr">
         <is>
           <t>Набор</t>
         </is>
       </c>
-      <c r="I51" s="12" t="n">
+      <c r="I51" s="15" t="n">
         <v>155.01</v>
       </c>
-      <c r="J51" s="12" t="n">
+      <c r="J51" s="15" t="n">
         <v>6975.45</v>
       </c>
     </row>
@@ -3721,7 +3815,7 @@
           <t>25.71.13.110-00000001</t>
         </is>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="G52" s="16" t="n">
         <v>170</v>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -3761,7 +3855,7 @@
           <t>20.52.10.190-00000005</t>
         </is>
       </c>
-      <c r="G53" s="13" t="n">
+      <c r="G53" s="16" t="n">
         <v>15</v>
       </c>
       <c r="H53" s="3" t="inlineStr">
@@ -3777,46 +3871,46 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B54" s="9" t="n">
+      <c r="B54" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C54" s="13" t="inlineStr">
         <is>
           <t>Картон канцелярский</t>
         </is>
       </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E54" s="9" t="inlineStr">
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
         <is>
           <t>17.23.14.120</t>
         </is>
       </c>
-      <c r="F54" s="9" t="inlineStr">
+      <c r="F54" s="12" t="inlineStr">
         <is>
           <t>17.23.14.120-00000003</t>
         </is>
       </c>
-      <c r="G54" s="11" t="n">
+      <c r="G54" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="H54" s="13" t="inlineStr">
         <is>
           <t>Упаковка</t>
         </is>
       </c>
-      <c r="I54" s="12" t="n">
+      <c r="I54" s="15" t="n">
         <v>832</v>
       </c>
-      <c r="J54" s="12" t="n">
+      <c r="J54" s="15" t="n">
         <v>832</v>
       </c>
     </row>
@@ -3845,7 +3939,7 @@
           <t>20.59.30.190-00000001</t>
         </is>
       </c>
-      <c r="G55" s="13" t="n">
+      <c r="G55" s="16" t="n">
         <v>20</v>
       </c>
       <c r="H55" s="3" t="inlineStr">
@@ -3885,7 +3979,7 @@
           <t>25.71.13.110-00000004</t>
         </is>
       </c>
-      <c r="G56" s="13" t="n">
+      <c r="G56" s="16" t="n">
         <v>100</v>
       </c>
       <c r="H56" s="3" t="inlineStr">
@@ -3901,42 +3995,42 @@
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B57" s="9" t="n">
+      <c r="B57" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C57" s="13" t="inlineStr">
         <is>
           <t>Набор ручек шариковых 4 цветов с прозрачным пластиковым корпусом и металлическим наконечником</t>
         </is>
       </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
         <is>
           <t>32.99.12.110</t>
         </is>
       </c>
-      <c r="F57" s="9" t="n"/>
-      <c r="G57" s="11" t="n">
+      <c r="F57" s="12" t="n"/>
+      <c r="G57" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="H57" s="10" t="inlineStr">
+      <c r="H57" s="13" t="inlineStr">
         <is>
           <t>Набор</t>
         </is>
       </c>
-      <c r="I57" s="12" t="n">
+      <c r="I57" s="15" t="n">
         <v>186.6</v>
       </c>
-      <c r="J57" s="12" t="n">
+      <c r="J57" s="15" t="n">
         <v>746.4</v>
       </c>
     </row>
@@ -3965,7 +4059,7 @@
           <t>28.23.12.110-00000001</t>
         </is>
       </c>
-      <c r="G58" s="13" t="n">
+      <c r="G58" s="16" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="3" t="inlineStr">
@@ -3981,178 +4075,178 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B59" s="9" t="n">
+      <c r="B59" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C59" s="13" t="inlineStr">
         <is>
           <t>Ручка канцелярская</t>
         </is>
       </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E59" s="9" t="inlineStr">
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
         <is>
           <t>32.99.12.110</t>
         </is>
       </c>
-      <c r="F59" s="9" t="inlineStr">
+      <c r="F59" s="12" t="inlineStr">
         <is>
           <t>32.99.12.110-00000008</t>
         </is>
       </c>
-      <c r="G59" s="11" t="n">
+      <c r="G59" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="H59" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I59" s="12" t="n">
+      <c r="H59" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I59" s="15" t="n">
         <v>15.21</v>
       </c>
-      <c r="J59" s="12" t="n">
+      <c r="J59" s="15" t="n">
         <v>912.6</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B60" s="9" t="n">
+      <c r="B60" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C60" s="13" t="inlineStr">
         <is>
           <t>Лоток для бумаги пластиковый</t>
         </is>
       </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F60" s="9" t="inlineStr">
+      <c r="F60" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000-00000016</t>
         </is>
       </c>
-      <c r="G60" s="11" t="n">
+      <c r="G60" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I60" s="12" t="n">
+      <c r="H60" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I60" s="15" t="n">
         <v>389</v>
       </c>
-      <c r="J60" s="12" t="n">
+      <c r="J60" s="15" t="n">
         <v>4668</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B61" s="9" t="n">
+      <c r="B61" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C61" s="13" t="inlineStr">
         <is>
           <t>Файл-вкладыш</t>
         </is>
       </c>
-      <c r="D61" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E61" s="9" t="inlineStr">
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F61" s="9" t="inlineStr">
+      <c r="F61" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000-00000013</t>
         </is>
       </c>
-      <c r="G61" s="11" t="n">
+      <c r="G61" s="14" t="n">
         <v>90</v>
       </c>
-      <c r="H61" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I61" s="12" t="n">
+      <c r="H61" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I61" s="15" t="n">
         <v>419.81</v>
       </c>
-      <c r="J61" s="12" t="n">
+      <c r="J61" s="15" t="n">
         <v>37782.9</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="inlineStr">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B62" s="9" t="n">
+      <c r="B62" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C62" s="13" t="inlineStr">
         <is>
           <t>Губка для маркерной доски</t>
         </is>
       </c>
-      <c r="D62" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E62" s="9" t="inlineStr">
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F62" s="9" t="inlineStr">
+      <c r="F62" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000-00000023</t>
         </is>
       </c>
-      <c r="G62" s="11" t="n">
+      <c r="G62" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="H62" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I62" s="12" t="n">
+      <c r="H62" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I62" s="15" t="n">
         <v>77.61</v>
       </c>
-      <c r="J62" s="12" t="n">
+      <c r="J62" s="15" t="n">
         <v>2328.3</v>
       </c>
     </row>
@@ -4181,7 +4275,7 @@
           <t>26.51.33.141-00000002</t>
         </is>
       </c>
-      <c r="G63" s="13" t="n">
+      <c r="G63" s="16" t="n">
         <v>155</v>
       </c>
       <c r="H63" s="3" t="inlineStr">
@@ -4197,134 +4291,134 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B64" s="9" t="n">
+      <c r="B64" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="C64" s="10" t="inlineStr">
+      <c r="C64" s="13" t="inlineStr">
         <is>
           <t>Карандаш механический</t>
         </is>
       </c>
-      <c r="D64" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E64" s="9" t="inlineStr">
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="inlineStr">
         <is>
           <t>32.99.12.130</t>
         </is>
       </c>
-      <c r="F64" s="9" t="inlineStr">
+      <c r="F64" s="12" t="inlineStr">
         <is>
           <t>32.99.12.130-00000005</t>
         </is>
       </c>
-      <c r="G64" s="11" t="n">
+      <c r="G64" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H64" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I64" s="12" t="n">
+      <c r="H64" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I64" s="15" t="n">
         <v>32.93</v>
       </c>
-      <c r="J64" s="12" t="n">
+      <c r="J64" s="15" t="n">
         <v>32.93</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B65" s="9" t="n">
+      <c r="B65" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="C65" s="13" t="inlineStr">
         <is>
           <t>Маркер</t>
         </is>
       </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E65" s="9" t="inlineStr">
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
         <is>
           <t>32.99.12.120</t>
         </is>
       </c>
-      <c r="F65" s="9" t="inlineStr">
+      <c r="F65" s="12" t="inlineStr">
         <is>
           <t>32.99.12.120-00000006</t>
         </is>
       </c>
-      <c r="G65" s="11" t="n">
+      <c r="G65" s="14" t="n">
         <v>54</v>
       </c>
-      <c r="H65" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I65" s="12" t="n">
+      <c r="H65" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I65" s="15" t="n">
         <v>30.43</v>
       </c>
-      <c r="J65" s="12" t="n">
+      <c r="J65" s="15" t="n">
         <v>1643.22</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B66" s="9" t="n">
+      <c r="B66" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C66" s="13" t="inlineStr">
         <is>
           <t>Пружина для переплета пластмассовая</t>
         </is>
       </c>
-      <c r="D66" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E66" s="9" t="inlineStr">
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F66" s="9" t="inlineStr">
+      <c r="F66" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000-00000032</t>
         </is>
       </c>
-      <c r="G66" s="11" t="n">
+      <c r="G66" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H66" s="10" t="inlineStr">
+      <c r="H66" s="13" t="inlineStr">
         <is>
           <t>Упаковка</t>
         </is>
       </c>
-      <c r="I66" s="12" t="n">
+      <c r="I66" s="15" t="n">
         <v>692</v>
       </c>
-      <c r="J66" s="12" t="n">
+      <c r="J66" s="15" t="n">
         <v>692</v>
       </c>
     </row>
@@ -4349,7 +4443,7 @@
         </is>
       </c>
       <c r="F67" s="6" t="n"/>
-      <c r="G67" s="13" t="n">
+      <c r="G67" s="16" t="n">
         <v>61</v>
       </c>
       <c r="H67" s="3" t="inlineStr">
@@ -4365,46 +4459,46 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B68" s="9" t="n">
+      <c r="B68" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="C68" s="10" t="inlineStr">
+      <c r="C68" s="13" t="inlineStr">
         <is>
           <t>Карандаш чернографитный</t>
         </is>
       </c>
-      <c r="D68" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E68" s="9" t="inlineStr">
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr">
         <is>
           <t>32.99.15.110</t>
         </is>
       </c>
-      <c r="F68" s="9" t="inlineStr">
+      <c r="F68" s="12" t="inlineStr">
         <is>
           <t>32.99.15.110-00000002</t>
         </is>
       </c>
-      <c r="G68" s="11" t="n">
+      <c r="G68" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I68" s="12" t="n">
+      <c r="H68" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I68" s="15" t="n">
         <v>6.92</v>
       </c>
-      <c r="J68" s="12" t="n">
+      <c r="J68" s="15" t="n">
         <v>1384</v>
       </c>
     </row>
@@ -4433,7 +4527,7 @@
           <t>22.29.21.000-00000002</t>
         </is>
       </c>
-      <c r="G69" s="13" t="n">
+      <c r="G69" s="16" t="n">
         <v>60</v>
       </c>
       <c r="H69" s="3" t="inlineStr">
@@ -4449,42 +4543,42 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="inlineStr">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B70" s="9" t="n">
+      <c r="B70" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="C70" s="10" t="inlineStr">
+      <c r="C70" s="13" t="inlineStr">
         <is>
           <t>Гель для увлажнения пальцев (канцелярский)</t>
         </is>
       </c>
-      <c r="D70" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E70" s="9" t="inlineStr">
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F70" s="9" t="n"/>
-      <c r="G70" s="11" t="n">
+      <c r="F70" s="12" t="n"/>
+      <c r="G70" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I70" s="12" t="n">
+      <c r="H70" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I70" s="15" t="n">
         <v>78.19</v>
       </c>
-      <c r="J70" s="12" t="n">
+      <c r="J70" s="15" t="n">
         <v>390.95</v>
       </c>
     </row>
@@ -4513,7 +4607,7 @@
           <t>22.19.73.120-00000002</t>
         </is>
       </c>
-      <c r="G71" s="13" t="n">
+      <c r="G71" s="16" t="n">
         <v>159</v>
       </c>
       <c r="H71" s="3" t="inlineStr">
@@ -4529,178 +4623,178 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="inlineStr">
+      <c r="A72" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B72" s="9" t="n">
+      <c r="B72" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="C72" s="10" t="inlineStr">
+      <c r="C72" s="13" t="inlineStr">
         <is>
           <t>Папка картонная</t>
         </is>
       </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E72" s="9" t="inlineStr">
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
         <is>
           <t>17.23.13.193</t>
         </is>
       </c>
-      <c r="F72" s="9" t="inlineStr">
+      <c r="F72" s="12" t="inlineStr">
         <is>
           <t>17.23.13.193-00000004</t>
         </is>
       </c>
-      <c r="G72" s="11" t="n">
+      <c r="G72" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="H72" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I72" s="12" t="n">
+      <c r="H72" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I72" s="15" t="n">
         <v>316.98</v>
       </c>
-      <c r="J72" s="12" t="n">
+      <c r="J72" s="15" t="n">
         <v>3169.8</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
+      <c r="A73" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B73" s="9" t="n">
+      <c r="B73" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="C73" s="10" t="inlineStr">
+      <c r="C73" s="13" t="inlineStr">
         <is>
           <t>Папка картонная</t>
         </is>
       </c>
-      <c r="D73" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E73" s="9" t="inlineStr">
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
         <is>
           <t>17.23.13.193</t>
         </is>
       </c>
-      <c r="F73" s="9" t="inlineStr">
+      <c r="F73" s="12" t="inlineStr">
         <is>
           <t>17.23.13.193-00000004</t>
         </is>
       </c>
-      <c r="G73" s="11" t="n">
+      <c r="G73" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="H73" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I73" s="12" t="n">
+      <c r="H73" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I73" s="15" t="n">
         <v>316.98</v>
       </c>
-      <c r="J73" s="12" t="n">
+      <c r="J73" s="15" t="n">
         <v>6339.6</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+      <c r="A74" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B74" s="9" t="n">
+      <c r="B74" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="C74" s="10" t="inlineStr">
+      <c r="C74" s="13" t="inlineStr">
         <is>
           <t>Блоки для записей</t>
         </is>
       </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E74" s="9" t="inlineStr">
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
         <is>
           <t>17.23.13.199</t>
         </is>
       </c>
-      <c r="F74" s="9" t="inlineStr">
+      <c r="F74" s="12" t="inlineStr">
         <is>
           <t>17.23.13.199-00000002</t>
         </is>
       </c>
-      <c r="G74" s="11" t="n">
+      <c r="G74" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="H74" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I74" s="12" t="n">
+      <c r="H74" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I74" s="15" t="n">
         <v>242.08</v>
       </c>
-      <c r="J74" s="12" t="n">
+      <c r="J74" s="15" t="n">
         <v>36312</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B75" s="9" t="n">
+      <c r="B75" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="C75" s="10" t="inlineStr">
+      <c r="C75" s="13" t="inlineStr">
         <is>
           <t>Папка пластиковая</t>
         </is>
       </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="inlineStr">
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F75" s="9" t="inlineStr">
+      <c r="F75" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000-00000009</t>
         </is>
       </c>
-      <c r="G75" s="11" t="n">
+      <c r="G75" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="H75" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I75" s="12" t="n">
+      <c r="H75" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I75" s="15" t="n">
         <v>171.39</v>
       </c>
-      <c r="J75" s="12" t="n">
+      <c r="J75" s="15" t="n">
         <v>3427.8</v>
       </c>
     </row>
@@ -4729,7 +4823,7 @@
           <t>22.19.73.120-00000004</t>
         </is>
       </c>
-      <c r="G76" s="13" t="n">
+      <c r="G76" s="16" t="n">
         <v>2</v>
       </c>
       <c r="H76" s="3" t="inlineStr">
@@ -4765,7 +4859,7 @@
         </is>
       </c>
       <c r="F77" s="6" t="n"/>
-      <c r="G77" s="13" t="n">
+      <c r="G77" s="16" t="n">
         <v>8</v>
       </c>
       <c r="H77" s="3" t="inlineStr">
@@ -4805,7 +4899,7 @@
           <t>22.29.21.000-00000002</t>
         </is>
       </c>
-      <c r="G78" s="13" t="n">
+      <c r="G78" s="16" t="n">
         <v>4</v>
       </c>
       <c r="H78" s="3" t="inlineStr">
@@ -4845,7 +4939,7 @@
           <t>22.19.71.190-00000090</t>
         </is>
       </c>
-      <c r="G79" s="13" t="n">
+      <c r="G79" s="16" t="n">
         <v>25</v>
       </c>
       <c r="H79" s="3" t="inlineStr">
@@ -4861,134 +4955,134 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="inlineStr">
+      <c r="A80" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B80" s="9" t="n">
+      <c r="B80" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="C80" s="10" t="inlineStr">
+      <c r="C80" s="13" t="inlineStr">
         <is>
           <t>Папка пластиковая</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E80" s="9" t="inlineStr">
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F80" s="9" t="inlineStr">
+      <c r="F80" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000-00000009</t>
         </is>
       </c>
-      <c r="G80" s="11" t="n">
+      <c r="G80" s="14" t="n">
         <v>220</v>
       </c>
-      <c r="H80" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I80" s="12" t="n">
+      <c r="H80" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I80" s="15" t="n">
         <v>42.18</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J80" s="15" t="n">
         <v>9279.6</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="inlineStr">
+      <c r="A81" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B81" s="9" t="n">
+      <c r="B81" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="C81" s="10" t="inlineStr">
+      <c r="C81" s="13" t="inlineStr">
         <is>
           <t>Блоки для записей</t>
         </is>
       </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E81" s="9" t="inlineStr">
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
         <is>
           <t>17.23.13.199</t>
         </is>
       </c>
-      <c r="F81" s="9" t="inlineStr">
+      <c r="F81" s="12" t="inlineStr">
         <is>
           <t>17.23.13.199-00000002</t>
         </is>
       </c>
-      <c r="G81" s="11" t="n">
+      <c r="G81" s="14" t="n">
         <v>310</v>
       </c>
-      <c r="H81" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I81" s="12" t="n">
+      <c r="H81" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I81" s="15" t="n">
         <v>34.09</v>
       </c>
-      <c r="J81" s="12" t="n">
+      <c r="J81" s="15" t="n">
         <v>10567.9</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="inlineStr">
+      <c r="A82" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B82" s="9" t="n">
+      <c r="B82" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="C82" s="10" t="inlineStr">
+      <c r="C82" s="13" t="inlineStr">
         <is>
           <t>Папка пластиковая</t>
         </is>
       </c>
-      <c r="D82" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E82" s="9" t="inlineStr">
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F82" s="9" t="inlineStr">
+      <c r="F82" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000-00000009</t>
         </is>
       </c>
-      <c r="G82" s="11" t="n">
+      <c r="G82" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="H82" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I82" s="12" t="n">
+      <c r="H82" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I82" s="15" t="n">
         <v>40.43</v>
       </c>
-      <c r="J82" s="12" t="n">
+      <c r="J82" s="15" t="n">
         <v>6064.5</v>
       </c>
     </row>
@@ -5017,7 +5111,7 @@
           <t>22.29.21.000-00000002</t>
         </is>
       </c>
-      <c r="G83" s="13" t="n">
+      <c r="G83" s="16" t="n">
         <v>100</v>
       </c>
       <c r="H83" s="3" t="inlineStr">
@@ -5033,46 +5127,46 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="inlineStr">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B84" s="9" t="n">
+      <c r="B84" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="C84" s="10" t="inlineStr">
+      <c r="C84" s="13" t="inlineStr">
         <is>
           <t>Грифель для карандаша механического</t>
         </is>
       </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
         <is>
           <t>32.99.15.120</t>
         </is>
       </c>
-      <c r="F84" s="9" t="inlineStr">
+      <c r="F84" s="12" t="inlineStr">
         <is>
           <t>32.99.15.120-00000001</t>
         </is>
       </c>
-      <c r="G84" s="11" t="n">
+      <c r="G84" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="H84" s="10" t="inlineStr">
+      <c r="H84" s="13" t="inlineStr">
         <is>
           <t>Упаковка</t>
         </is>
       </c>
-      <c r="I84" s="12" t="n">
+      <c r="I84" s="15" t="n">
         <v>8.09</v>
       </c>
-      <c r="J84" s="12" t="n">
+      <c r="J84" s="15" t="n">
         <v>647.2</v>
       </c>
     </row>
@@ -5101,7 +5195,7 @@
           <t>22.19.73.120-00000004</t>
         </is>
       </c>
-      <c r="G85" s="13" t="n">
+      <c r="G85" s="16" t="n">
         <v>1</v>
       </c>
       <c r="H85" s="3" t="inlineStr">
@@ -5141,7 +5235,7 @@
           <t>25.71.11.120-00000004</t>
         </is>
       </c>
-      <c r="G86" s="13" t="n">
+      <c r="G86" s="16" t="n">
         <v>100</v>
       </c>
       <c r="H86" s="3" t="inlineStr">
@@ -5177,7 +5271,7 @@
         </is>
       </c>
       <c r="F87" s="6" t="n"/>
-      <c r="G87" s="13" t="n">
+      <c r="G87" s="16" t="n">
         <v>3</v>
       </c>
       <c r="H87" s="3" t="inlineStr">
@@ -5217,7 +5311,7 @@
           <t>20.59.59.900-00000001</t>
         </is>
       </c>
-      <c r="G88" s="13" t="n">
+      <c r="G88" s="16" t="n">
         <v>260</v>
       </c>
       <c r="H88" s="3" t="inlineStr">
@@ -5233,90 +5327,90 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="inlineStr">
+      <c r="A89" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B89" s="9" t="n">
+      <c r="B89" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="C89" s="10" t="inlineStr">
+      <c r="C89" s="13" t="inlineStr">
         <is>
           <t>Папка пластиковая</t>
         </is>
       </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E89" s="9" t="inlineStr">
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F89" s="9" t="inlineStr">
+      <c r="F89" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000-00000009</t>
         </is>
       </c>
-      <c r="G89" s="11" t="n">
+      <c r="G89" s="14" t="n">
         <v>90</v>
       </c>
-      <c r="H89" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I89" s="12" t="n">
+      <c r="H89" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I89" s="15" t="n">
         <v>113.42</v>
       </c>
-      <c r="J89" s="12" t="n">
+      <c r="J89" s="15" t="n">
         <v>10207.8</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="inlineStr">
+      <c r="A90" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B90" s="9" t="n">
+      <c r="B90" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="C90" s="10" t="inlineStr">
+      <c r="C90" s="13" t="inlineStr">
         <is>
           <t>Папка пластиковая</t>
         </is>
       </c>
-      <c r="D90" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E90" s="9" t="inlineStr">
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F90" s="9" t="inlineStr">
+      <c r="F90" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000-00000009</t>
         </is>
       </c>
-      <c r="G90" s="11" t="n">
+      <c r="G90" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="H90" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I90" s="12" t="n">
+      <c r="H90" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I90" s="15" t="n">
         <v>51.02</v>
       </c>
-      <c r="J90" s="12" t="n">
+      <c r="J90" s="15" t="n">
         <v>4081.6</v>
       </c>
     </row>
@@ -5345,7 +5439,7 @@
           <t>20.52.10.190-00000003</t>
         </is>
       </c>
-      <c r="G91" s="13" t="n">
+      <c r="G91" s="16" t="n">
         <v>160</v>
       </c>
       <c r="H91" s="3" t="inlineStr">
@@ -5361,46 +5455,46 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="inlineStr">
+      <c r="A92" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B92" s="9" t="n">
+      <c r="B92" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="C92" s="10" t="inlineStr">
+      <c r="C92" s="13" t="inlineStr">
         <is>
           <t>Папка картонная</t>
         </is>
       </c>
-      <c r="D92" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E92" s="9" t="inlineStr">
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr">
         <is>
           <t>17.23.13.193</t>
         </is>
       </c>
-      <c r="F92" s="9" t="inlineStr">
+      <c r="F92" s="12" t="inlineStr">
         <is>
           <t>17.23.13.193-00000004</t>
         </is>
       </c>
-      <c r="G92" s="11" t="n">
+      <c r="G92" s="14" t="n">
         <v>170</v>
       </c>
-      <c r="H92" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I92" s="12" t="n">
+      <c r="H92" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I92" s="15" t="n">
         <v>316.98</v>
       </c>
-      <c r="J92" s="12" t="n">
+      <c r="J92" s="15" t="n">
         <v>53886.6</v>
       </c>
     </row>
@@ -5429,7 +5523,7 @@
           <t>20.52.10.190-00000007</t>
         </is>
       </c>
-      <c r="G93" s="13" t="n">
+      <c r="G93" s="16" t="n">
         <v>10</v>
       </c>
       <c r="H93" s="3" t="inlineStr">
@@ -5445,46 +5539,46 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="inlineStr">
+      <c r="A94" s="11" t="inlineStr">
         <is>
           <t>0367100008826000022</t>
         </is>
       </c>
-      <c r="B94" s="9" t="n">
+      <c r="B94" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="C94" s="10" t="inlineStr">
+      <c r="C94" s="13" t="inlineStr">
         <is>
           <t>Клейкие закладки пластиковые</t>
         </is>
       </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E94" s="9" t="inlineStr">
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000</t>
         </is>
       </c>
-      <c r="F94" s="9" t="inlineStr">
+      <c r="F94" s="12" t="inlineStr">
         <is>
           <t>22.29.25.000-00000002</t>
         </is>
       </c>
-      <c r="G94" s="11" t="n">
+      <c r="G94" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="H94" s="10" t="inlineStr">
+      <c r="H94" s="13" t="inlineStr">
         <is>
           <t>Упаковка</t>
         </is>
       </c>
-      <c r="I94" s="12" t="n">
+      <c r="I94" s="15" t="n">
         <v>36.59</v>
       </c>
-      <c r="J94" s="12" t="n">
+      <c r="J94" s="15" t="n">
         <v>10977</v>
       </c>
     </row>
@@ -5513,7 +5607,7 @@
           <t>17.21.13.000-00000001</t>
         </is>
       </c>
-      <c r="G95" s="13" t="n">
+      <c r="G95" s="16" t="n">
         <v>12</v>
       </c>
       <c r="H95" s="3" t="inlineStr">
@@ -5553,7 +5647,7 @@
           <t>17.21.13.000-00000001</t>
         </is>
       </c>
-      <c r="G96" s="13" t="n">
+      <c r="G96" s="16" t="n">
         <v>27</v>
       </c>
       <c r="H96" s="3" t="inlineStr">
@@ -5593,7 +5687,7 @@
           <t>17.21.13.000-00000001</t>
         </is>
       </c>
-      <c r="G97" s="13" t="n">
+      <c r="G97" s="16" t="n">
         <v>12</v>
       </c>
       <c r="H97" s="3" t="inlineStr">
@@ -5609,1006 +5703,1006 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="inlineStr">
+      <c r="A98" s="11" t="inlineStr">
         <is>
           <t>0367100008826000023</t>
         </is>
       </c>
-      <c r="B98" s="9" t="n">
+      <c r="B98" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="C98" s="10" t="inlineStr">
+      <c r="C98" s="13" t="inlineStr">
         <is>
           <t>Журнал (книга) регистрации и учета специализированный</t>
         </is>
       </c>
-      <c r="D98" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E98" s="9" t="inlineStr">
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="inlineStr">
         <is>
           <t>17.23.13.110</t>
         </is>
       </c>
-      <c r="F98" s="9" t="inlineStr">
+      <c r="F98" s="12" t="inlineStr">
         <is>
           <t>17.23.13.110-00000001</t>
         </is>
       </c>
-      <c r="G98" s="11" t="n">
+      <c r="G98" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="H98" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I98" s="12" t="n">
+      <c r="H98" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I98" s="15" t="n">
         <v>306.39</v>
       </c>
-      <c r="J98" s="12" t="n">
+      <c r="J98" s="15" t="n">
         <v>3676.68</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="8" t="inlineStr">
+      <c r="A99" s="11" t="inlineStr">
         <is>
           <t>0367100008826000023</t>
         </is>
       </c>
-      <c r="B99" s="9" t="n">
+      <c r="B99" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="C99" s="10" t="inlineStr">
+      <c r="C99" s="13" t="inlineStr">
         <is>
           <t>Расшиватель для скоб</t>
         </is>
       </c>
-      <c r="D99" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E99" s="9" t="inlineStr">
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="inlineStr">
         <is>
           <t>25.99.22.130</t>
         </is>
       </c>
-      <c r="F99" s="9" t="inlineStr">
+      <c r="F99" s="12" t="inlineStr">
         <is>
           <t>25.99.22.130-00000005</t>
         </is>
       </c>
-      <c r="G99" s="11" t="n">
+      <c r="G99" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="H99" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I99" s="12" t="n">
+      <c r="H99" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I99" s="15" t="n">
         <v>38.51</v>
       </c>
-      <c r="J99" s="12" t="n">
+      <c r="J99" s="15" t="n">
         <v>2310.6</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="inlineStr">
+      <c r="A100" s="11" t="inlineStr">
         <is>
           <t>0367100008826000023</t>
         </is>
       </c>
-      <c r="B100" s="9" t="n">
+      <c r="B100" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C100" s="10" t="inlineStr">
+      <c r="C100" s="13" t="inlineStr">
         <is>
           <t>Дырокол</t>
         </is>
       </c>
-      <c r="D100" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E100" s="9" t="inlineStr">
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
         <is>
           <t>25.99.22.130</t>
         </is>
       </c>
-      <c r="F100" s="9" t="inlineStr">
+      <c r="F100" s="12" t="inlineStr">
         <is>
           <t>25.99.22.130-00000002</t>
         </is>
       </c>
-      <c r="G100" s="11" t="n">
+      <c r="G100" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="H100" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I100" s="12" t="n">
+      <c r="H100" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I100" s="15" t="n">
         <v>429.23</v>
       </c>
-      <c r="J100" s="12" t="n">
+      <c r="J100" s="15" t="n">
         <v>3004.61</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="inlineStr">
+      <c r="A101" s="11" t="inlineStr">
         <is>
           <t>0367100008826000023</t>
         </is>
       </c>
-      <c r="B101" s="9" t="n">
+      <c r="B101" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="C101" s="10" t="inlineStr">
+      <c r="C101" s="13" t="inlineStr">
         <is>
           <t>Зажим для бумаг</t>
         </is>
       </c>
-      <c r="D101" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E101" s="9" t="inlineStr">
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000</t>
         </is>
       </c>
-      <c r="F101" s="9" t="inlineStr">
+      <c r="F101" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000-00000022</t>
         </is>
       </c>
-      <c r="G101" s="11" t="n">
+      <c r="G101" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="H101" s="10" t="inlineStr">
+      <c r="H101" s="13" t="inlineStr">
         <is>
           <t>Упаковка</t>
         </is>
       </c>
-      <c r="I101" s="12" t="n">
+      <c r="I101" s="15" t="n">
         <v>21.38</v>
       </c>
-      <c r="J101" s="12" t="n">
+      <c r="J101" s="15" t="n">
         <v>2138</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="8" t="inlineStr">
+      <c r="A102" s="11" t="inlineStr">
         <is>
           <t>0367100008826000023</t>
         </is>
       </c>
-      <c r="B102" s="9" t="n">
+      <c r="B102" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="C102" s="10" t="inlineStr">
+      <c r="C102" s="13" t="inlineStr">
         <is>
           <t>Зажим для бумаг</t>
         </is>
       </c>
-      <c r="D102" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E102" s="9" t="inlineStr">
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000</t>
         </is>
       </c>
-      <c r="F102" s="9" t="inlineStr">
+      <c r="F102" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000-00000022</t>
         </is>
       </c>
-      <c r="G102" s="11" t="n">
+      <c r="G102" s="14" t="n">
         <v>90</v>
       </c>
-      <c r="H102" s="10" t="inlineStr">
+      <c r="H102" s="13" t="inlineStr">
         <is>
           <t>Упаковка</t>
         </is>
       </c>
-      <c r="I102" s="12" t="n">
+      <c r="I102" s="15" t="n">
         <v>28.3</v>
       </c>
-      <c r="J102" s="12" t="n">
+      <c r="J102" s="15" t="n">
         <v>2547</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="8" t="inlineStr">
+      <c r="A103" s="11" t="inlineStr">
         <is>
           <t>0367100008826000023</t>
         </is>
       </c>
-      <c r="B103" s="9" t="n">
+      <c r="B103" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="C103" s="10" t="inlineStr">
+      <c r="C103" s="13" t="inlineStr">
         <is>
           <t>Зажим для бумаг</t>
         </is>
       </c>
-      <c r="D103" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E103" s="9" t="inlineStr">
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000</t>
         </is>
       </c>
-      <c r="F103" s="9" t="inlineStr">
+      <c r="F103" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000-00000022</t>
         </is>
       </c>
-      <c r="G103" s="11" t="n">
+      <c r="G103" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="H103" s="10" t="inlineStr">
+      <c r="H103" s="13" t="inlineStr">
         <is>
           <t>Упаковка</t>
         </is>
       </c>
-      <c r="I103" s="12" t="n">
+      <c r="I103" s="15" t="n">
         <v>47.18</v>
       </c>
-      <c r="J103" s="12" t="n">
+      <c r="J103" s="15" t="n">
         <v>3302.6</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="8" t="inlineStr">
+      <c r="A104" s="11" t="inlineStr">
         <is>
           <t>0367100008826000023</t>
         </is>
       </c>
-      <c r="B104" s="9" t="n">
+      <c r="B104" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="C104" s="10" t="inlineStr">
+      <c r="C104" s="13" t="inlineStr">
         <is>
           <t>Зажим для бумаг</t>
         </is>
       </c>
-      <c r="D104" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E104" s="9" t="inlineStr">
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000</t>
         </is>
       </c>
-      <c r="F104" s="9" t="inlineStr">
+      <c r="F104" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000-00000022</t>
         </is>
       </c>
-      <c r="G104" s="11" t="n">
+      <c r="G104" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="H104" s="10" t="inlineStr">
+      <c r="H104" s="13" t="inlineStr">
         <is>
           <t>Упаковка</t>
         </is>
       </c>
-      <c r="I104" s="12" t="n">
+      <c r="I104" s="15" t="n">
         <v>70.48</v>
       </c>
-      <c r="J104" s="12" t="n">
+      <c r="J104" s="15" t="n">
         <v>4933.6</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="8" t="inlineStr">
+      <c r="A105" s="11" t="inlineStr">
         <is>
           <t>0367100008826000023</t>
         </is>
       </c>
-      <c r="B105" s="9" t="n">
+      <c r="B105" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="C105" s="10" t="inlineStr">
+      <c r="C105" s="13" t="inlineStr">
         <is>
           <t>Зажим для бумаг</t>
         </is>
       </c>
-      <c r="D105" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E105" s="9" t="inlineStr">
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000</t>
         </is>
       </c>
-      <c r="F105" s="9" t="inlineStr">
+      <c r="F105" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000-00000022</t>
         </is>
       </c>
-      <c r="G105" s="11" t="n">
+      <c r="G105" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="H105" s="10" t="inlineStr">
+      <c r="H105" s="13" t="inlineStr">
         <is>
           <t>Упаковка</t>
         </is>
       </c>
-      <c r="I105" s="12" t="n">
+      <c r="I105" s="15" t="n">
         <v>109.58</v>
       </c>
-      <c r="J105" s="12" t="n">
+      <c r="J105" s="15" t="n">
         <v>7670.6</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="8" t="inlineStr">
+      <c r="A106" s="11" t="inlineStr">
         <is>
           <t>0367100008826000023</t>
         </is>
       </c>
-      <c r="B106" s="9" t="n">
+      <c r="B106" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="C106" s="10" t="inlineStr">
+      <c r="C106" s="13" t="inlineStr">
         <is>
           <t>Зажим для бумаг</t>
         </is>
       </c>
-      <c r="D106" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E106" s="9" t="inlineStr">
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000</t>
         </is>
       </c>
-      <c r="F106" s="9" t="inlineStr">
+      <c r="F106" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000-00000022</t>
         </is>
       </c>
-      <c r="G106" s="11" t="n">
+      <c r="G106" s="14" t="n">
         <v>66</v>
       </c>
-      <c r="H106" s="10" t="inlineStr">
+      <c r="H106" s="13" t="inlineStr">
         <is>
           <t>Упаковка</t>
         </is>
       </c>
-      <c r="I106" s="12" t="n">
+      <c r="I106" s="15" t="n">
         <v>186.6</v>
       </c>
-      <c r="J106" s="12" t="n">
+      <c r="J106" s="15" t="n">
         <v>12315.6</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="8" t="inlineStr">
+      <c r="A107" s="11" t="inlineStr">
         <is>
           <t>0367100008826000023</t>
         </is>
       </c>
-      <c r="B107" s="9" t="n">
+      <c r="B107" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="C107" s="10" t="inlineStr">
+      <c r="C107" s="13" t="inlineStr">
         <is>
           <t>Игла металлическая для прошивки документов</t>
         </is>
       </c>
-      <c r="D107" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E107" s="9" t="inlineStr">
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000</t>
         </is>
       </c>
-      <c r="F107" s="9" t="n"/>
-      <c r="G107" s="11" t="n">
+      <c r="F107" s="12" t="n"/>
+      <c r="G107" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H107" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I107" s="12" t="n">
+      <c r="H107" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I107" s="15" t="n">
         <v>42.18</v>
       </c>
-      <c r="J107" s="12" t="n">
+      <c r="J107" s="15" t="n">
         <v>42.18</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="inlineStr">
+      <c r="A108" s="11" t="inlineStr">
         <is>
           <t>0367100008826000023</t>
         </is>
       </c>
-      <c r="B108" s="9" t="n">
+      <c r="B108" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="C108" s="10" t="inlineStr">
+      <c r="C108" s="13" t="inlineStr">
         <is>
           <t>Кнопки канцелярские</t>
         </is>
       </c>
-      <c r="D108" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E108" s="9" t="inlineStr">
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000</t>
         </is>
       </c>
-      <c r="F108" s="9" t="n"/>
-      <c r="G108" s="11" t="n">
+      <c r="F108" s="12" t="n"/>
+      <c r="G108" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="H108" s="10" t="inlineStr">
+      <c r="H108" s="13" t="inlineStr">
         <is>
           <t>Упаковка</t>
         </is>
       </c>
-      <c r="I108" s="12" t="n">
+      <c r="I108" s="15" t="n">
         <v>28.89</v>
       </c>
-      <c r="J108" s="12" t="n">
+      <c r="J108" s="15" t="n">
         <v>462.24</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="8" t="inlineStr">
+      <c r="A109" s="11" t="inlineStr">
         <is>
           <t>0367100008826000023</t>
         </is>
       </c>
-      <c r="B109" s="9" t="n">
+      <c r="B109" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="C109" s="10" t="inlineStr">
+      <c r="C109" s="13" t="inlineStr">
         <is>
           <t>Скобы для степлера</t>
         </is>
       </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E109" s="9" t="inlineStr">
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000</t>
         </is>
       </c>
-      <c r="F109" s="9" t="inlineStr">
+      <c r="F109" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000-00000018</t>
         </is>
       </c>
-      <c r="G109" s="11" t="n">
+      <c r="G109" s="14" t="n">
         <v>350</v>
       </c>
-      <c r="H109" s="10" t="inlineStr">
+      <c r="H109" s="13" t="inlineStr">
         <is>
           <t>Упаковка</t>
         </is>
       </c>
-      <c r="I109" s="12" t="n">
+      <c r="I109" s="15" t="n">
         <v>20.22</v>
       </c>
-      <c r="J109" s="12" t="n">
+      <c r="J109" s="15" t="n">
         <v>7077</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="8" t="inlineStr">
+      <c r="A110" s="11" t="inlineStr">
         <is>
           <t>0367100008826000023</t>
         </is>
       </c>
-      <c r="B110" s="9" t="n">
+      <c r="B110" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="C110" s="10" t="inlineStr">
+      <c r="C110" s="13" t="inlineStr">
         <is>
           <t>Скобы для степлера</t>
         </is>
       </c>
-      <c r="D110" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E110" s="9" t="inlineStr">
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000</t>
         </is>
       </c>
-      <c r="F110" s="9" t="inlineStr">
+      <c r="F110" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000-00000007</t>
         </is>
       </c>
-      <c r="G110" s="11" t="n">
+      <c r="G110" s="14" t="n">
         <v>139</v>
       </c>
-      <c r="H110" s="10" t="inlineStr">
+      <c r="H110" s="13" t="inlineStr">
         <is>
           <t>Упаковка</t>
         </is>
       </c>
-      <c r="I110" s="12" t="n">
+      <c r="I110" s="15" t="n">
         <v>39.1</v>
       </c>
-      <c r="J110" s="12" t="n">
+      <c r="J110" s="15" t="n">
         <v>5434.9</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="8" t="inlineStr">
+      <c r="A111" s="11" t="inlineStr">
         <is>
           <t>0367100008826000023</t>
         </is>
       </c>
-      <c r="B111" s="9" t="n">
+      <c r="B111" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="C111" s="10" t="inlineStr">
+      <c r="C111" s="13" t="inlineStr">
         <is>
           <t>Скрепки металлические</t>
         </is>
       </c>
-      <c r="D111" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E111" s="9" t="inlineStr">
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000</t>
         </is>
       </c>
-      <c r="F111" s="9" t="inlineStr">
+      <c r="F111" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000-00000020</t>
         </is>
       </c>
-      <c r="G111" s="11" t="n">
+      <c r="G111" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="H111" s="10" t="inlineStr">
+      <c r="H111" s="13" t="inlineStr">
         <is>
           <t>Упаковка</t>
         </is>
       </c>
-      <c r="I111" s="12" t="n">
+      <c r="I111" s="15" t="n">
         <v>26.38</v>
       </c>
-      <c r="J111" s="12" t="n">
+      <c r="J111" s="15" t="n">
         <v>5276</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="8" t="inlineStr">
+      <c r="A112" s="11" t="inlineStr">
         <is>
           <t>0367100008826000023</t>
         </is>
       </c>
-      <c r="B112" s="9" t="n">
+      <c r="B112" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="C112" s="10" t="inlineStr">
+      <c r="C112" s="13" t="inlineStr">
         <is>
           <t>Скрепки металлические</t>
         </is>
       </c>
-      <c r="D112" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E112" s="9" t="inlineStr">
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000</t>
         </is>
       </c>
-      <c r="F112" s="9" t="inlineStr">
+      <c r="F112" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000-00000020</t>
         </is>
       </c>
-      <c r="G112" s="11" t="n">
+      <c r="G112" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="H112" s="10" t="inlineStr">
+      <c r="H112" s="13" t="inlineStr">
         <is>
           <t>Упаковка</t>
         </is>
       </c>
-      <c r="I112" s="12" t="n">
+      <c r="I112" s="15" t="n">
         <v>43.52</v>
       </c>
-      <c r="J112" s="12" t="n">
+      <c r="J112" s="15" t="n">
         <v>870.4</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="8" t="inlineStr">
+      <c r="A113" s="11" t="inlineStr">
         <is>
           <t>0367100008826000023</t>
         </is>
       </c>
-      <c r="B113" s="9" t="n">
+      <c r="B113" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="C113" s="10" t="inlineStr">
+      <c r="C113" s="13" t="inlineStr">
         <is>
           <t>Степлер</t>
         </is>
       </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E113" s="9" t="inlineStr">
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
         <is>
           <t>25.99.22.130</t>
         </is>
       </c>
-      <c r="F113" s="9" t="inlineStr">
+      <c r="F113" s="12" t="inlineStr">
         <is>
           <t>25.99.22.130-00000006</t>
         </is>
       </c>
-      <c r="G113" s="11" t="n">
+      <c r="G113" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="H113" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I113" s="12" t="n">
+      <c r="H113" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I113" s="15" t="n">
         <v>92.04000000000001</v>
       </c>
-      <c r="J113" s="12" t="n">
+      <c r="J113" s="15" t="n">
         <v>9204</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="8" t="inlineStr">
+      <c r="A114" s="11" t="inlineStr">
         <is>
           <t>0367100008826000023</t>
         </is>
       </c>
-      <c r="B114" s="9" t="n">
+      <c r="B114" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="C114" s="10" t="inlineStr">
+      <c r="C114" s="13" t="inlineStr">
         <is>
           <t>Степлер</t>
         </is>
       </c>
-      <c r="D114" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E114" s="9" t="inlineStr">
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E114" s="12" t="inlineStr">
         <is>
           <t>25.99.22.130</t>
         </is>
       </c>
-      <c r="F114" s="9" t="inlineStr">
+      <c r="F114" s="12" t="inlineStr">
         <is>
           <t>25.99.22.130-00000006</t>
         </is>
       </c>
-      <c r="G114" s="11" t="n">
+      <c r="G114" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="H114" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I114" s="12" t="n">
+      <c r="H114" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I114" s="15" t="n">
         <v>173.89</v>
       </c>
-      <c r="J114" s="12" t="n">
+      <c r="J114" s="15" t="n">
         <v>10433.4</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="8" t="inlineStr">
+      <c r="A115" s="11" t="inlineStr">
         <is>
           <t>0367100008826000023</t>
         </is>
       </c>
-      <c r="B115" s="9" t="n">
+      <c r="B115" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="C115" s="10" t="inlineStr">
+      <c r="C115" s="13" t="inlineStr">
         <is>
           <t>Шило канцелярское</t>
         </is>
       </c>
-      <c r="D115" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E115" s="9" t="inlineStr">
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000</t>
         </is>
       </c>
-      <c r="F115" s="9" t="inlineStr">
+      <c r="F115" s="12" t="inlineStr">
         <is>
           <t>25.99.23.000-00000025</t>
         </is>
       </c>
-      <c r="G115" s="11" t="n">
+      <c r="G115" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="H115" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I115" s="12" t="n">
+      <c r="H115" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I115" s="15" t="n">
         <v>102.07</v>
       </c>
-      <c r="J115" s="12" t="n">
+      <c r="J115" s="15" t="n">
         <v>816.5599999999999</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="8" t="inlineStr">
+      <c r="A116" s="11" t="inlineStr">
         <is>
           <t>0367100008826000023</t>
         </is>
       </c>
-      <c r="B116" s="9" t="n">
+      <c r="B116" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="C116" s="10" t="inlineStr">
+      <c r="C116" s="13" t="inlineStr">
         <is>
           <t>Конверт почтовый бумажный</t>
         </is>
       </c>
-      <c r="D116" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E116" s="9" t="inlineStr">
+      <c r="D116" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="inlineStr">
         <is>
           <t>17.23.12.110</t>
         </is>
       </c>
-      <c r="F116" s="9" t="inlineStr">
+      <c r="F116" s="12" t="inlineStr">
         <is>
           <t>17.23.12.110-00000002</t>
         </is>
       </c>
-      <c r="G116" s="11" t="n">
+      <c r="G116" s="14" t="n">
         <v>1000</v>
       </c>
-      <c r="H116" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I116" s="12" t="n">
+      <c r="H116" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I116" s="15" t="n">
         <v>12.71</v>
       </c>
-      <c r="J116" s="12" t="n">
+      <c r="J116" s="15" t="n">
         <v>12710</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="8" t="inlineStr">
+      <c r="A117" s="11" t="inlineStr">
         <is>
           <t>0367100008826000023</t>
         </is>
       </c>
-      <c r="B117" s="9" t="n">
+      <c r="B117" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="C117" s="10" t="inlineStr">
+      <c r="C117" s="13" t="inlineStr">
         <is>
           <t>Конверт почтовый бумажный</t>
         </is>
       </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E117" s="9" t="inlineStr">
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
         <is>
           <t>17.23.12.110</t>
         </is>
       </c>
-      <c r="F117" s="9" t="inlineStr">
+      <c r="F117" s="12" t="inlineStr">
         <is>
           <t>17.23.12.110-00000002</t>
         </is>
       </c>
-      <c r="G117" s="11" t="n">
+      <c r="G117" s="14" t="n">
         <v>600</v>
       </c>
-      <c r="H117" s="10" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="I117" s="12" t="n">
+      <c r="H117" s="13" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="I117" s="15" t="n">
         <v>4.04</v>
       </c>
-      <c r="J117" s="12" t="n">
+      <c r="J117" s="15" t="n">
         <v>2424</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="8" t="inlineStr">
+      <c r="A118" s="11" t="inlineStr">
         <is>
           <t>0167300017626000036</t>
         </is>
       </c>
-      <c r="B118" s="9" t="n">
+      <c r="B118" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C118" s="10" t="inlineStr">
+      <c r="C118" s="13" t="inlineStr">
         <is>
           <t>Бумага для офисной техники</t>
         </is>
       </c>
-      <c r="D118" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E118" s="9" t="inlineStr">
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="inlineStr">
         <is>
           <t>17.12.14.110</t>
         </is>
       </c>
-      <c r="F118" s="9" t="inlineStr">
+      <c r="F118" s="12" t="inlineStr">
         <is>
           <t>17.12.14.110-00000005</t>
         </is>
       </c>
-      <c r="G118" s="11" t="n">
+      <c r="G118" s="14" t="n">
         <v>450</v>
       </c>
-      <c r="H118" s="10" t="inlineStr">
+      <c r="H118" s="13" t="inlineStr">
         <is>
           <t>Пачка</t>
         </is>
       </c>
-      <c r="I118" s="12" t="n">
+      <c r="I118" s="15" t="n">
         <v>357.3</v>
       </c>
-      <c r="J118" s="12" t="n">
+      <c r="J118" s="15" t="n">
         <v>160785</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="8" t="inlineStr">
+      <c r="A119" s="11" t="inlineStr">
         <is>
           <t>0367100010426000074</t>
         </is>
       </c>
-      <c r="B119" s="9" t="n">
+      <c r="B119" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C119" s="10" t="inlineStr">
+      <c r="C119" s="13" t="inlineStr">
         <is>
           <t>Бумага для офисной техники</t>
         </is>
       </c>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E119" s="9" t="inlineStr">
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
         <is>
           <t>17.12.14.110</t>
         </is>
       </c>
-      <c r="F119" s="9" t="inlineStr">
+      <c r="F119" s="12" t="inlineStr">
         <is>
           <t>17.12.14.110-00000005</t>
         </is>
       </c>
-      <c r="G119" s="11" t="n">
+      <c r="G119" s="14" t="n">
         <v>500</v>
       </c>
-      <c r="H119" s="10" t="inlineStr">
+      <c r="H119" s="13" t="inlineStr">
         <is>
           <t>Пачка</t>
         </is>
       </c>
-      <c r="I119" s="12" t="n">
+      <c r="I119" s="15" t="n">
         <v>379.02</v>
       </c>
-      <c r="J119" s="12" t="n">
+      <c r="J119" s="15" t="n">
         <v>189510</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="8" t="inlineStr">
+      <c r="A120" s="11" t="inlineStr">
         <is>
           <t>0367100000926000059</t>
         </is>
       </c>
-      <c r="B120" s="9" t="n">
+      <c r="B120" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C120" s="10" t="inlineStr">
+      <c r="C120" s="13" t="inlineStr">
         <is>
           <t>Бумага для офисной техники</t>
         </is>
       </c>
-      <c r="D120" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E120" s="9" t="inlineStr">
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="E120" s="12" t="inlineStr">
         <is>
           <t>17.12.14.110</t>
         </is>
       </c>
-      <c r="F120" s="9" t="inlineStr">
+      <c r="F120" s="12" t="inlineStr">
         <is>
           <t>17.12.14.110-00000004</t>
         </is>
       </c>
-      <c r="G120" s="11" t="n">
+      <c r="G120" s="14" t="n">
         <v>2170</v>
       </c>
-      <c r="H120" s="10" t="inlineStr">
+      <c r="H120" s="13" t="inlineStr">
         <is>
           <t>Пачка</t>
         </is>
       </c>
-      <c r="I120" s="12" t="n">
+      <c r="I120" s="15" t="n">
         <v>310</v>
       </c>
-      <c r="J120" s="12" t="n">
+      <c r="J120" s="15" t="n">
         <v>672700</v>
       </c>
     </row>
@@ -6755,175 +6849,175 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>Закупки по профилю «Канцтовары и бумага — Тюмень»</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Сформировано 03.10.2026 в 12:00 по данным zakupki.gov.ru</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>Что искали</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>Регионы</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Тюменская область</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Период размещения</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>01.09.2026 – 03.10.2026</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>любой</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>Ключевые слова</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>канцеляр* товар*, канцтовар*, бумага офисн*, "бумага для офисной техники", ручка шариков*, степлер</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Минус-слова</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>ремонт*, заправк*, обслуживан*</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>ОКПД2</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>17.12.14, 17.23, 22.29.25, 25.99.22, 25.99.23, 32.99.12, 32.99.15</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>КТРУ</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Только заказчики (ИНН)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>любые</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>Кроме заказчиков (ИНН)</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Начальная цена</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>любая</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Итоги</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Проверено закупок</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="20" t="n">
         <v>128</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Подошло</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
+      <c r="B18" s="20" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>Как читать отчёт</t>
         </is>
